--- a/13774_Cuenca_Jequetepeque/_raw_reportes_xlsx/IDConfig_67640_completo.xlsx
+++ b/13774_Cuenca_Jequetepeque/_raw_reportes_xlsx/IDConfig_67640_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R9778a4e1e5ac4d2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rf6e755a52c544eb0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3908</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4882</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5896</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8049</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6595</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6951</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5048</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3679</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5896</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.4088</x:v>
+        <x:v>      2.6418</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +429,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.3275</x:v>
+        <x:v>      2.5896</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +444,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.3275</x:v>
+        <x:v>      2.5896</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +459,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.3275</x:v>
+        <x:v>      2.5896</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +474,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.4502</x:v>
+        <x:v>      2.6951</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -354,7 +489,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.4088</x:v>
+        <x:v>      2.6595</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,7 +504,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.5133</x:v>
+        <x:v>      2.7495</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +519,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.4711</x:v>
+        <x:v>      2.7131</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -399,7 +534,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.6210</x:v>
+        <x:v>      2.8425</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -414,7 +549,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.6429</x:v>
+        <x:v>      2.8615</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +564,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.5560</x:v>
+        <x:v>      2.7863</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -444,7 +579,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.7320</x:v>
+        <x:v>      2.9387</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -459,7 +594,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.7773</x:v>
+        <x:v>      2.9781</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -474,7 +609,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.9167</x:v>
+        <x:v>      3.0995</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -489,7 +624,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.8697</x:v>
+        <x:v>      3.0585</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -504,7 +639,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.9167</x:v>
+        <x:v>      3.0995</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -519,7 +654,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.9167</x:v>
+        <x:v>      3.0995</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -534,7 +669,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.0368</x:v>
+        <x:v>      3.2044</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -549,7 +684,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.1106</x:v>
+        <x:v>      3.2691</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -564,7 +699,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.0125</x:v>
+        <x:v>      3.1831</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -579,7 +714,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.9643</x:v>
+        <x:v>      3.1410</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -594,42 +729,42 @@
         </x:is>
       </x:c>
       <x:c s="3">
+        <x:v>      3.1202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0382</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
         <x:v>      3.9404</x:v>
       </x:c>
     </x:row>
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>22/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.8464</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      3.9404</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
           <x:t>20/07/2026</x:t>
         </x:is>
       </x:c>
@@ -639,7 +774,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.0125</x:v>
+        <x:v>      3.1831</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -654,7 +789,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.0125</x:v>
+        <x:v>      3.1831</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -669,7 +804,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.0368</x:v>
+        <x:v>      3.2044</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/13774_Cuenca_Jequetepeque/_raw_reportes_xlsx/IDConfig_67640_completo.xlsx
+++ b/13774_Cuenca_Jequetepeque/_raw_reportes_xlsx/IDConfig_67640_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rf6e755a52c544eb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rc341bedea1644470"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.4254</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.1624</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.2477</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9983</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2670</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2222</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5556</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4231</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5556</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7498</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7681</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6597</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0184</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9196</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7681</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3282</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4070</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1928</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0110</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1638</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2222</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4070</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3282</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3751</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3282</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2670</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2520</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3751</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4070</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3594</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3594</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3751</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4719</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2670</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2074</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1782</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0791</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0379</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1069</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0929</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1352</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2370</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4719</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5556</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5218</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2670</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2821</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3127</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.3908</x:v>
+        <x:v>      2.3910</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -279,7 +999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.4882</x:v>
+        <x:v>      2.4884</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +1014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.5896</x:v>
+        <x:v>      2.5899</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +1029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.8049</x:v>
+        <x:v>      2.8052</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +1044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.6595</x:v>
+        <x:v>      2.6597</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +1059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.6951</x:v>
+        <x:v>      2.6954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -354,7 +1074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.5048</x:v>
+        <x:v>      2.5051</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,7 +1089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.3679</x:v>
+        <x:v>      2.5556</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +1104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.5896</x:v>
+        <x:v>      2.5899</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -399,7 +1119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.6418</x:v>
+        <x:v>      2.6421</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -414,7 +1134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.2875</x:v>
+        <x:v>      2.5386</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +1149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.5896</x:v>
+        <x:v>      2.5899</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -444,7 +1164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.5896</x:v>
+        <x:v>      2.5899</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -459,7 +1179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.5896</x:v>
+        <x:v>      2.5899</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -474,7 +1194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.6951</x:v>
+        <x:v>      2.6954</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -489,7 +1209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.6595</x:v>
+        <x:v>      2.6597</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -504,7 +1224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.7495</x:v>
+        <x:v>      2.7498</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -519,7 +1239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.7131</x:v>
+        <x:v>      2.7134</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -534,7 +1254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.8425</x:v>
+        <x:v>      2.8428</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -549,7 +1269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.8615</x:v>
+        <x:v>      2.8618</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -564,7 +1284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.7863</x:v>
+        <x:v>      2.7866</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -579,7 +1299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.9387</x:v>
+        <x:v>      2.9391</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -594,7 +1314,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.9781</x:v>
+        <x:v>      2.9784</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -609,7 +1329,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.0995</x:v>
+        <x:v>      3.0998</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -624,7 +1344,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.0585</x:v>
+        <x:v>      3.0588</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -639,7 +1359,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.0995</x:v>
+        <x:v>      3.0998</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -654,7 +1374,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.0995</x:v>
+        <x:v>      3.0998</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -669,7 +1389,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.2044</x:v>
+        <x:v>      3.2047</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -684,7 +1404,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.2691</x:v>
+        <x:v>      3.2694</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -699,7 +1419,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.1831</x:v>
+        <x:v>      3.1835</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -714,7 +1434,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.1410</x:v>
+        <x:v>      3.1414</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -729,7 +1449,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.1202</x:v>
+        <x:v>      3.1205</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -744,7 +1464,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.0382</x:v>
+        <x:v>      3.0385</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -759,7 +1479,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.9404</x:v>
+        <x:v>      3.0793</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -774,7 +1494,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.1831</x:v>
+        <x:v>      3.1835</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -789,7 +1509,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.1831</x:v>
+        <x:v>      3.1835</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -804,7 +1524,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.2044</x:v>
+        <x:v>      3.2047</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -819,7 +1539,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.0368</x:v>
+        <x:v>      3.2047</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -834,7 +1554,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.1355</x:v>
+        <x:v>      3.2912</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -849,7 +1569,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.2366</x:v>
+        <x:v>      3.3801</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -864,7 +1584,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.4732</x:v>
+        <x:v>      3.5888</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -879,7 +1599,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.8931</x:v>
+        <x:v>      3.0793</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -894,7 +1614,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.0612</x:v>
+        <x:v>      3.2262</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -909,7 +1629,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.0125</x:v>
+        <x:v>      3.1835</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -924,7 +1644,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.0858</x:v>
+        <x:v>      3.2477</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -939,7 +1659,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.9883</x:v>
+        <x:v>      3.1624</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -954,7 +1674,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.1605</x:v>
+        <x:v>      3.3132</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -969,7 +1689,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.7230</x:v>
+        <x:v>      3.8104</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -984,7 +1704,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.9868</x:v>
+        <x:v>      4.0456</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -999,7 +1719,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.4195</x:v>
+        <x:v>      3.5413</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1014,7 +1734,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.3929</x:v>
+        <x:v>      3.5178</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1029,7 +1749,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.5550</x:v>
+        <x:v>      3.6612</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1044,7 +1764,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.6103</x:v>
+        <x:v>      3.7102</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1059,7 +1779,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.4732</x:v>
+        <x:v>      3.5888</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1074,7 +1794,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.5550</x:v>
+        <x:v>      3.6612</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1089,7 +1809,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.7230</x:v>
+        <x:v>      3.8104</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1104,7 +1824,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.8678</x:v>
+        <x:v>      3.9393</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1119,7 +1839,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.9270</x:v>
+        <x:v>      3.9921</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1134,7 +1854,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.8385</x:v>
+        <x:v>      3.9132</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1149,7 +1869,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.9868</x:v>
+        <x:v>      4.0456</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1164,7 +1884,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.9868</x:v>
+        <x:v>      4.9020</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1179,7 +1899,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.9270</x:v>
+        <x:v>      4.7378</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1194,7 +1914,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.9270</x:v>
+        <x:v>      4.7378</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1209,7 +1929,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.0170</x:v>
+        <x:v>      4.9848</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1239,7 +1959,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.1708</x:v>
+        <x:v>      5.4053</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1254,7 +1974,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.0780</x:v>
+        <x:v>      5.1517</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1269,43 +1989,193 @@
         </x:is>
       </x:c>
       <x:c s="3">
+        <x:v>      5.6630</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.5767</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.4908</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
         <x:v>      5.3203</x:v>
       </x:c>
     </x:row>
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>16/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.2337</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.2022</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/06/2026</x:t>
+          <x:t>13/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.4908</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8370</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8370</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.1013</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6630</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.4053</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6630</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0128</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5508</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/06/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -1320,22 +2190,67 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>13/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.2022</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/06/2026</x:t>
+          <x:t>03/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.7498</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.7498</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.9247</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.5767</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/05/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -1350,97 +2265,97 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>11/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.8370</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.1013</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.6630</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.4053</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.6630</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.0128</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/06/2026</x:t>
+          <x:t>29/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.3203</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.9247</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.1903</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.2798</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.7498</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.4600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/05/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -1455,201 +2370,6 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>04/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.4908</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.7498</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.7498</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.9247</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>31/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.5767</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.8370</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.3203</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.9247</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.1903</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.2798</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      5.7498</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.4600</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.5508</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
           <x:t>22/05/2026</x:t>
         </x:is>
       </x:c>
@@ -1674,7 +2394,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.3486</x:v>
+        <x:v>      8.0639</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1704,7 +2424,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     11.8872</x:v>
+        <x:v>      8.6607</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1884,7 +2604,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     18.7171</x:v>
+        <x:v>     17.2051</x:v>
       </x:c>
     </x:row>
     <x:row>
